--- a/originales/respuestas/2025/01. Calificadas/bucle p33/Secretaría Distrital De Integración Social.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p33/Secretaría Distrital De Integración Social.xlsx
@@ -484,7 +484,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -500,6 +500,11 @@
       <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -584,7 +589,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -607,6 +612,7 @@
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -822,8 +828,9 @@
   <cols>
     <col customWidth="1" min="1" max="3" width="10.71"/>
     <col customWidth="1" min="4" max="4" width="24.14"/>
-    <col customWidth="1" min="5" max="6" width="10.71"/>
-    <col customWidth="1" min="7" max="7" width="16.29"/>
+    <col customWidth="1" min="5" max="5" width="10.71"/>
+    <col customWidth="1" min="6" max="6" width="23.71"/>
+    <col customWidth="1" min="7" max="7" width="24.14"/>
     <col customWidth="1" min="8" max="8" width="20.57"/>
     <col customWidth="1" min="9" max="31" width="10.71"/>
   </cols>
@@ -3490,7 +3497,12 @@
       <c r="AD46" s="7"/>
       <c r="AE46" s="7"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="F47" s="8">
+        <f>SUM(F2:F46)</f>
+        <v>628908</v>
+      </c>
+    </row>
     <row r="48" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
